--- a/data/Pending_Tasks.xlsx
+++ b/data/Pending_Tasks.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Landing Page" sheetId="1" state="visible" r:id="rId2"/>
@@ -30,38 +30,59 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="55">
   <si>
     <t xml:space="preserve">Task Detail</t>
   </si>
   <si>
+    <t xml:space="preserve">Task Status</t>
+  </si>
+  <si>
     <t xml:space="preserve">Remove the Ayurveda word from login page </t>
   </si>
   <si>
+    <t xml:space="preserve">DONE</t>
+  </si>
+  <si>
     <t xml:space="preserve">login page should be in light mode</t>
   </si>
   <si>
     <t xml:space="preserve">Back to shopping should be removed from the current place right side and should be placed as Shop Now button in left side</t>
   </si>
   <si>
+    <t xml:space="preserve">Remove the text “we will email” . Just say one time password will be sent to the below email id , please enter correct email address.</t>
+  </si>
+  <si>
     <t xml:space="preserve">One solid image instead of the slide bar, which shows all the details about sarveda</t>
   </si>
   <si>
     <t xml:space="preserve">first image should occupy 70% hegiht  of screen and remaining should start from there</t>
   </si>
   <si>
+    <t xml:space="preserve">remove ayurveda from logo section in all pages ,we are not doing ayurveda anymore</t>
+  </si>
+  <si>
     <t xml:space="preserve">remove svaram sound ships from database</t>
   </si>
   <si>
     <t xml:space="preserve">Header, sidebar should be fixed, customer should be able to scroll the products without pagination , so remove pagination  in shop products section, each product header in left should have different color from its child elements, imptove the coloring , also make the sound instruments as the first priority, make eco living as final. By default sound instruments should be expanded, others can be closed, on customer click it can open. We should have filter options </t>
   </si>
   <si>
+    <t xml:space="preserve">Remove below section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make the left section tree fixed , and right section content scrollable , I mean the page is fixed </t>
+  </si>
+  <si>
     <t xml:space="preserve">Available offers should appear in PDP page like Welcome 10 , in case its expired, dont show it</t>
   </si>
   <si>
     <t xml:space="preserve">Pairing items should be current woocommerece, tell me how you have done now</t>
   </si>
   <si>
+    <t xml:space="preserve">PENDING</t>
+  </si>
+  <si>
     <t xml:space="preserve">related articles should be shown for each product if it exists, it should be shown in PDP </t>
   </si>
   <si>
@@ -80,6 +101,9 @@
     <t xml:space="preserve">When a customer makes a review his country flag should be displayed ,along with country in the review section, along with rating, comments and stars</t>
   </si>
   <si>
+    <t xml:space="preserve">Country flag is not appearing for the reviews </t>
+  </si>
+  <si>
     <t xml:space="preserve">Genberated invoice phone number and address should be chnaged</t>
   </si>
   <si>
@@ -89,15 +113,9 @@
     <t xml:space="preserve">Notes should be removed in invoice</t>
   </si>
   <si>
-    <t xml:space="preserve">Task Status</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pass the address details to stripe</t>
   </si>
   <si>
-    <t xml:space="preserve">DONE</t>
-  </si>
-  <si>
     <t xml:space="preserve">Show all countries in checkout</t>
   </si>
   <si>
@@ -152,7 +170,13 @@
     <t xml:space="preserve">Other marketplaces like amazon, amala, firstcry orders should be tracked from the admin panel in future – this is stage 2 task</t>
   </si>
   <si>
+    <t xml:space="preserve">STAGE 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">AD management  should be done – consult with Rahul – This is my task , you dont do anything</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MY TASK</t>
   </si>
   <si>
     <t xml:space="preserve">Admin should be able to add , video, image, audio for each product, i think for now we have audio and image, so video upload is pending , Each of these should be separate of each variant and not general so move it to variant section</t>
@@ -180,7 +204,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -207,6 +231,13 @@
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
@@ -326,7 +357,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -339,11 +370,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -351,27 +386,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -453,18 +488,18 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>451800</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>142560</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>977400</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>9000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="Image 1" descr=""/>
+        <xdr:cNvPr id="0" name="Image 2" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -473,8 +508,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="609480"/>
-          <a:ext cx="17493120" cy="4848120"/>
+          <a:off x="0" y="1560960"/>
+          <a:ext cx="6621120" cy="3085560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -489,35 +524,132 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>451440</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>142200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Image 1" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="609480"/>
+          <a:ext cx="17682840" cy="4847760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>765720</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>94680</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Image 3" descr=""/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5800680"/>
+          <a:ext cx="17997120" cy="2037960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>3</v>
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="44.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -528,6 +660,7 @@
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -536,19 +669,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="79.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
+      <c r="A2" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -566,120 +703,172 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
-        <v>27</v>
+      <c r="A2" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
-        <v>28</v>
+      <c r="A3" s="12" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
-        <v>29</v>
+      <c r="A4" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
-        <v>30</v>
+      <c r="A5" s="12" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
-        <v>31</v>
+      <c r="A6" s="11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>32</v>
+      <c r="A7" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>33</v>
+      <c r="A8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>34</v>
+      <c r="A9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
-        <v>35</v>
+      <c r="A10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>36</v>
+      <c r="A11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
-        <v>37</v>
+      <c r="A12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>38</v>
+      <c r="A13" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
-        <v>39</v>
+      <c r="A14" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>40</v>
+      <c r="A15" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
-        <v>41</v>
+      <c r="A16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>42</v>
+      <c r="A17" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>43</v>
+      <c r="A18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="4" t="s">
-        <v>44</v>
+      <c r="A19" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>45</v>
+      <c r="A20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="4" t="s">
-        <v>44</v>
+      <c r="A21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>46</v>
+      <c r="A22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -705,26 +894,40 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>4</v>
+      <c r="A2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>5</v>
+      <c r="A3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -743,25 +946,45 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B43"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>6</v>
+      <c r="A2" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>7</v>
+      <c r="A3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -781,10 +1004,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.37"/>
   </cols>
   <sheetData>
@@ -792,45 +1017,75 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>8</v>
+      <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>9</v>
+      <c r="A3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>10</v>
+      <c r="A4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
+      <c r="A5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>12</v>
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>13</v>
+      <c r="A7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
-        <v>14</v>
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>15</v>
+      <c r="A9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -849,30 +1104,43 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" s="6" customFormat="true" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>16</v>
+      <c r="A2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>17</v>
+      <c r="A3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>18</v>
+      <c r="A4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -892,10 +1160,10 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -903,47 +1171,55 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>21</v>
+      <c r="A2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="8"/>
+      <c r="A3" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="9"/>
+      <c r="A4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="8"/>
+      <c r="A5" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="9"/>
+      <c r="A6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>21</v>
+      <c r="A7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -962,19 +1238,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="79.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
+      <c r="A2" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -992,19 +1272,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="79.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
+      <c r="A2" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1022,19 +1306,23 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="79.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
+      <c r="A2" s="4"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/data/Pending_Tasks.xlsx
+++ b/data/Pending_Tasks.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Landing Page" sheetId="1" state="visible" r:id="rId2"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="63">
   <si>
     <t xml:space="preserve">Task Detail</t>
   </si>
@@ -195,6 +195,30 @@
   </si>
   <si>
     <t xml:space="preserve">For each course we are dispalying the fees at the outer card , remove it, customer should see it insid the details page </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparation time – default field should be kept for admin, when the stock goes zero , customer will be notified of the same, each product will have its own preparation time, do it according to the vartiant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Express shipping and surafce shipping should be shown as text in PDP, only show the buttons in checkout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Making the purchase for an item based on the movemenet of order</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whatsapp messaging strealine </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger a message to customer , after the delivery, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coupon codes – should be shown product wise, and bring to 5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum 2500 – free shipping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMI avaliable for orders above “”</t>
   </si>
 </sst>
 </file>
@@ -493,9 +517,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>977400</xdr:colOff>
+      <xdr:colOff>977040</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>9000</xdr:rowOff>
+      <xdr:rowOff>8640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -509,7 +533,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="1560960"/>
-          <a:ext cx="6621120" cy="3085560"/>
+          <a:ext cx="6620400" cy="3085200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -535,9 +559,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>451440</xdr:colOff>
+      <xdr:colOff>451080</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>142200</xdr:rowOff>
+      <xdr:rowOff>141840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -551,7 +575,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="609480"/>
-          <a:ext cx="17682840" cy="4847760"/>
+          <a:ext cx="17699040" cy="4847400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -572,9 +596,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>765720</xdr:colOff>
+      <xdr:colOff>765360</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>94680</xdr:rowOff>
+      <xdr:rowOff>94320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -588,7 +612,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="5800680"/>
-          <a:ext cx="17997120" cy="2037960"/>
+          <a:ext cx="18013320" cy="2037600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -609,7 +633,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -670,7 +694,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -703,8 +727,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B30"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -823,7 +847,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
         <v>50</v>
       </c>
@@ -863,12 +887,52 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="42.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -895,7 +959,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.01"/>
@@ -947,7 +1011,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1005,11 +1069,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.37"/>
   </cols>
   <sheetData>
@@ -1105,7 +1169,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1160,7 +1224,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.01"/>
@@ -1239,7 +1303,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1273,7 +1337,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1307,7 +1371,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>

--- a/data/Pending_Tasks.xlsx
+++ b/data/Pending_Tasks.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="65">
   <si>
     <t xml:space="preserve">Task Detail</t>
   </si>
@@ -219,6 +219,12 @@
   </si>
   <si>
     <t xml:space="preserve">EMI avaliable for orders above “”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chnage the invoice phone number to 9535975075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Send Full country name to Zoho API, Due on receipt to paid or  handle COD appropriately. MRP should be removed, HSN code missing              </t>
   </si>
 </sst>
 </file>
@@ -517,9 +523,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>977040</xdr:colOff>
+      <xdr:colOff>976680</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>8640</xdr:rowOff>
+      <xdr:rowOff>8280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -533,7 +539,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="1560960"/>
-          <a:ext cx="6620400" cy="3085200"/>
+          <a:ext cx="6620040" cy="3084840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -559,9 +565,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>451080</xdr:colOff>
+      <xdr:colOff>450720</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>141840</xdr:rowOff>
+      <xdr:rowOff>141480</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -575,7 +581,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="609480"/>
-          <a:ext cx="17699040" cy="4847400"/>
+          <a:ext cx="17715240" cy="4847040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -596,9 +602,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>765360</xdr:colOff>
+      <xdr:colOff>765000</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>94320</xdr:rowOff>
+      <xdr:rowOff>93960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -612,7 +618,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="5800680"/>
-          <a:ext cx="18013320" cy="2037600"/>
+          <a:ext cx="18029520" cy="2037240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -633,7 +639,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -694,7 +700,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -727,8 +733,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -933,6 +939,16 @@
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -959,7 +975,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.01"/>
@@ -1011,7 +1027,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1069,11 +1085,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40.15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.37"/>
   </cols>
   <sheetData>
@@ -1169,7 +1185,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1224,7 +1240,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.01"/>
@@ -1303,7 +1319,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1337,7 +1353,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1371,7 +1387,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>

--- a/data/Pending_Tasks.xlsx
+++ b/data/Pending_Tasks.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Landing Page" sheetId="1" state="visible" r:id="rId2"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="65">
   <si>
     <t xml:space="preserve">Task Detail</t>
   </si>
@@ -518,60 +518,18 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>976680</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>8280</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="Image 2" descr=""/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="1560960"/>
-          <a:ext cx="6620040" cy="3084840"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>450720</xdr:colOff>
+      <xdr:colOff>450000</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>141480</xdr:rowOff>
+      <xdr:rowOff>140760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Image 1" descr=""/>
+        <xdr:cNvPr id="0" name="Image 1" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -581,7 +539,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="609480"/>
-          <a:ext cx="17715240" cy="4847040"/>
+          <a:ext cx="17747280" cy="4846320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -602,13 +560,13 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>765000</xdr:colOff>
+      <xdr:colOff>764280</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:rowOff>93240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 3" descr=""/>
+        <xdr:cNvPr id="1" name="Image 3" descr=""/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -618,7 +576,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="5800680"/>
-          <a:ext cx="18029520" cy="2037240"/>
+          <a:ext cx="18061560" cy="2036520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -639,7 +597,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -677,9 +635,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="51.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>6</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -690,7 +651,6 @@
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -700,7 +660,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -734,7 +694,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -975,7 +935,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.01"/>
@@ -1027,7 +987,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1085,7 +1045,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1185,7 +1145,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1240,7 +1200,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.01"/>
@@ -1319,7 +1279,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1353,7 +1313,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1387,7 +1347,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>

--- a/data/Pending_Tasks.xlsx
+++ b/data/Pending_Tasks.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Landing Page" sheetId="1" state="visible" r:id="rId2"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="69">
   <si>
     <t xml:space="preserve">Task Detail</t>
   </si>
@@ -74,6 +74,9 @@
     <t xml:space="preserve">Make the left section tree fixed , and right section content scrollable , I mean the page is fixed </t>
   </si>
   <si>
+    <t xml:space="preserve">Whatsapp messages should be sent as standard templates with buttons for actions, dont use the phonen umerbs instead use the brand nasme</t>
+  </si>
+  <si>
     <t xml:space="preserve">Available offers should appear in PDP page like Welcome 10 , in case its expired, dont show it</t>
   </si>
   <si>
@@ -225,6 +228,15 @@
   </si>
   <si>
     <t xml:space="preserve">Send Full country name to Zoho API, Due on receipt to paid or  handle COD appropriately. MRP should be removed, HSN code missing              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adding products wshould allow the admin to add the variant names and sub categories (multiple levels dynamic)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For product category allow the admin to drag and change the position to allow the customers to see top selling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For all products section adapt the same</t>
   </si>
 </sst>
 </file>
@@ -523,9 +535,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>450000</xdr:colOff>
+      <xdr:colOff>449640</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>140760</xdr:rowOff>
+      <xdr:rowOff>140400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -539,7 +551,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="609480"/>
-          <a:ext cx="17747280" cy="4846320"/>
+          <a:ext cx="17763480" cy="4845960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -560,9 +572,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>764280</xdr:colOff>
+      <xdr:colOff>763920</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>93240</xdr:rowOff>
+      <xdr:rowOff>92880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -576,7 +588,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="5800680"/>
-          <a:ext cx="18061560" cy="2036520"/>
+          <a:ext cx="18077760" cy="2036160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -597,7 +609,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -660,7 +672,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -693,8 +705,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -710,7 +722,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>3</v>
@@ -718,32 +730,32 @@
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>3</v>
@@ -751,7 +763,7 @@
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>3</v>
@@ -759,7 +771,7 @@
     </row>
     <row r="10" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" s="0" t="s">
         <v>3</v>
@@ -767,7 +779,7 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="0" t="s">
         <v>3</v>
@@ -775,71 +787,71 @@
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20" s="0" t="s">
         <v>3</v>
@@ -847,15 +859,15 @@
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="42.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B22" s="0" t="s">
         <v>3</v>
@@ -863,52 +875,67 @@
     </row>
     <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -935,7 +962,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.01"/>
@@ -986,8 +1013,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B44"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1025,6 +1052,11 @@
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1045,7 +1077,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1063,7 +1095,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>3</v>
@@ -1071,15 +1103,15 @@
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>3</v>
@@ -1087,7 +1119,7 @@
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5" s="0" t="s">
         <v>3</v>
@@ -1095,7 +1127,7 @@
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B6" s="0" t="s">
         <v>3</v>
@@ -1103,7 +1135,7 @@
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="0" t="s">
         <v>3</v>
@@ -1111,7 +1143,7 @@
     </row>
     <row r="8" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="0" t="s">
         <v>3</v>
@@ -1119,13 +1151,13 @@
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="0" t="s">
         <v>3</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1177,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1161,7 +1193,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>3</v>
@@ -1169,7 +1201,7 @@
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" s="0" t="s">
         <v>3</v>
@@ -1177,7 +1209,7 @@
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>3</v>
@@ -1200,7 +1232,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.01"/>
@@ -1216,7 +1248,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>3</v>
@@ -1224,7 +1256,7 @@
     </row>
     <row r="3" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>3</v>
@@ -1232,7 +1264,7 @@
     </row>
     <row r="4" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>3</v>
@@ -1240,7 +1272,7 @@
     </row>
     <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>3</v>
@@ -1248,7 +1280,7 @@
     </row>
     <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>3</v>
@@ -1256,7 +1288,7 @@
     </row>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>3</v>
@@ -1279,7 +1311,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1313,7 +1345,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1347,7 +1379,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>

--- a/data/Pending_Tasks.xlsx
+++ b/data/Pending_Tasks.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="68">
   <si>
     <t xml:space="preserve">Task Detail</t>
   </si>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">Making the purchase for an item based on the movemenet of order</t>
   </si>
   <si>
-    <t xml:space="preserve">Whatsapp messaging strealine </t>
+    <t xml:space="preserve">Whatsapp messaging streamline </t>
   </si>
   <si>
     <t xml:space="preserve">Trigger a message to customer , after the delivery, </t>
@@ -227,10 +227,7 @@
     <t xml:space="preserve">Chnage the invoice phone number to 9535975075</t>
   </si>
   <si>
-    <t xml:space="preserve">Send Full country name to Zoho API, Due on receipt to paid or  handle COD appropriately. MRP should be removed, HSN code missing              </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adding products wshould allow the admin to add the variant names and sub categories (multiple levels dynamic)</t>
+    <t xml:space="preserve">Adding products should allow the admin to add the variant names and sub categories (multiple levels dynamic)</t>
   </si>
   <si>
     <t xml:space="preserve">For product category allow the admin to drag and change the position to allow the customers to see top selling</t>
@@ -535,9 +532,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>449640</xdr:colOff>
+      <xdr:colOff>448920</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>140400</xdr:rowOff>
+      <xdr:rowOff>139680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -551,44 +548,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="609480"/>
-          <a:ext cx="17763480" cy="4845960"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>763920</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>92880</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Image 3" descr=""/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch/>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="5800680"/>
-          <a:ext cx="18077760" cy="2036160"/>
+          <a:ext cx="17787600" cy="4845240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -609,7 +569,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -672,7 +632,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -705,10 +665,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B35"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B1048576"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="93.59"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
   </cols>
   <sheetData>
@@ -873,17 +833,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="18.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>58</v>
       </c>
@@ -933,11 +893,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="Introduce the Role based access, add below email ids as admin for now"/>
@@ -962,7 +918,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.01"/>
@@ -995,6 +951,9 @@
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1013,8 +972,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B1048576"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1049,16 +1008,30 @@
         <v>12</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+    <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
+    <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="1048563" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048564" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048565" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048566" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048567" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
@@ -1077,7 +1050,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1177,7 +1150,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1232,7 +1205,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.01"/>
@@ -1270,7 +1243,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="33.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
@@ -1278,7 +1251,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="40.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>32</v>
       </c>
@@ -1311,7 +1284,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1345,7 +1318,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
@@ -1379,7 +1352,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="79.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.01"/>
